--- a/Streamlit/Data/defined_processes.xlsx
+++ b/Streamlit/Data/defined_processes.xlsx
@@ -413,226 +413,202 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Categorization</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Categorization</t>
+          <t>Word</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Word</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
           <t>Definition</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>69</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
           <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>70</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
           <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>145</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
           <t>Desired State Metrics: Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>147</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
           <t>Current State Analysis: Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>149</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
           <t>Root Cause Assessment: Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>151</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
           <t>Historical Overview: Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>153</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
           <t>Baseline Metrics (Current State): Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>71</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Data Collection</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
-        <is>
-          <t>Data Collection</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
         <is>
           <t>Data collection involves identifying, sourcing, and acquiring the datasets required to solve the defined problem. This may include internal databases, APIs, logs, third-party data, or manually collected data. Key considerations include data availability, coverage, granularity, freshness, and legal or privacy constraints. The quality and relevance of collected data fundamentally limit the ceiling of model performance.
 Need to understand the data available to solve a problem, insure that it's documented, understood and trusted. Need to identify, not only information which is available, but information which is not available and should be.  This should be explicitly documented, referenced constantly and readily available (Semantic and Functional Definition).</t>
@@ -640,25 +616,22 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>72</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Data Preparation</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>Data Preparation</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
         <is>
           <t>Data preparation focuses on cleaning and structuring raw data into a usable format for modeling. This includes handling missing values, correcting errors, standardizing formats, encoding categorical variables, and aligning labels with features. It also often involves train/validation/test splitting to prevent data leakage. This step is critical because most models assume clean, well-structured inputs and are highly sensitive to data issues.
 Need to establish up a consistent, robust and repeatable data ingestion process, which starts at the outset of the project. Where the infrastructure is not immediately available, need to clearly document the journey.  Need to call out requirements, expectations and limitations, and where resources are necessary, they should be identified at this point. 
@@ -667,25 +640,22 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>73</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Exploratory Data Analysis</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
-        <is>
-          <t>Exploratory Data Analysis</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
         <is>
           <t xml:space="preserve">Foundational step in ensuring the success of a machine learning model—and, by extension, the overall project. Its purpose is to confirm that the data is appropriately structured, consistent, and of sufficient quality to support reliable modeling.
 While every dataset and project is unique, applying a consistent EDA approach helps reduce the laborious and time-consuming nature of data preparation. A structured process enables quicker identification of data issues, improves understanding of key variables and relationships, and creates a more stable foundation for subsequent modeling decisions. </t>
@@ -693,50 +663,44 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>74</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Feature Engineering</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Feature Engineering</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
           <t>Process of creating new input variables that better represent the underlying patterns in the data. It may include transformations (log, scaling), aggregations, interactions, temporal features, or domain-specific encodings. Effective feature engineering can significantly improve model performance even with simple algorithms. It embeds domain knowledge into the model and often provides more value than algorithmic complexity.  It is often one of the most impactful steps in the machine learning workflow.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>75</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Feature Selection</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
-        <is>
-          <t>Feature Selection</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
         <is>
           <t>Process of identifying and retaining the most relevant variables for model training while removing redundant, noisy, or irrelevant features. This helps reduce overfitting, improve model performance, and increase interpretability. Feature selection techniques may be statistical, model-based, or embedded within the learning algorithm. The goal is to create a simpler, more robust feature set that generalizes well to new data.
 It is important to be in a position to Logically and Mathematically be in a position to defend inclusion and exclusion decisions. Although a highly technical step, it is critically important that stakeholders and partners are included and in references and terms which are appropriate for them.</t>
@@ -744,563 +708,494 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>76</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>77</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
           <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>78</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Hyperparameter Tuning</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Hyperparameter Tuning</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
           <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>79</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Model Evaluation</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Model Evaluation</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
           <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>80</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Validation</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
           <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>81</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
           <t>Model Interpretability</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>82</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Deployment</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
           <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>83</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Monitoring</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
           <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>84</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Bias, Fairness, and Ethics</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Bias, Fairness, and Ethics</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
           <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>18</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Baseline Metrics (Current State)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Baseline Metrics (Current State)</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
           <t>Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>15</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Current State Analysis</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Current State Analysis</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
           <t>Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>14</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Desired State Metrics</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Desired State Metrics</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
           <t>Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>17</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Historical Overview</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Historical Overview</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
           <t>Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
-        <v>16</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Root Cause Assessment</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Root Cause Assessment</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
           <t>Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>49</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
           <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
-        <v>50</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
           <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>144</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
           <t>Desired State Metrics: Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>146</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
           <t>Current State Analysis: Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
-        <v>148</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
           <t>Root Cause Assessment: Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
-        <v>150</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
           <t>Historical Overview: Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
-        <v>152</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
           <t>Baseline Metrics (Current State): Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
-        <v>51</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
           <t>Current State Assessment</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>52</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Data Collection</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
-        <is>
-          <t>Data Collection</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
         <is>
           <t>Data collection involves identifying, sourcing, and acquiring the datasets required to solve the defined problem. This may include internal databases, APIs, logs, third-party data, or manually collected data. Key considerations include data availability, coverage, granularity, freshness, and legal or privacy constraints. The quality and relevance of collected data fundamentally limit the ceiling of model performance.
 Need to understand the data available to solve a problem, insure that it's documented, understood and trusted. Need to identify, not only information which is available, but information which is not available and should be.  This should be explicitly documented, referenced constantly and readily available (Semantic and Functional Definition).</t>
@@ -1308,323 +1203,278 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
-        <v>53</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
           <t>Root Cause Analysis</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="n">
-        <v>54</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
           <t>Research and Exploration</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="n">
-        <v>55</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
           <t>Option Generation</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="n">
-        <v>56</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
           <t>Solution Design</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="n">
-        <v>57</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
           <t>Feasibility Assessment</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="n">
-        <v>58</v>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
           <t>Prioritization and Decision Making</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="n">
-        <v>59</v>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
           <t>Implementation Planning</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="n">
-        <v>60</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
           <t>Execution</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="n">
-        <v>61</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
           <t>Testing and Validation</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="n">
-        <v>62</v>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
           <t>Evaluation</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="n">
-        <v>63</v>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
           <t>Optimization</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" t="n">
-        <v>64</v>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
           <t>Documentation and Knowledge Sharing</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="n">
-        <v>65</v>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Monitoring</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
           <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="n">
-        <v>66</v>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
           <t>Continuous Improvement</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="n">
-        <v>67</v>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
           <t>Governance, Risk, and Ethics</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Streamlit/Data/defined_processes.xlsx
+++ b/Streamlit/Data/defined_processes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -652,38 +652,38 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>Data Preparation</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Function cleans, reshapes, filters, joins, or transforms data into usable form.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>Exploratory Data Analysis</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t xml:space="preserve">Foundational step in ensuring the success of a machine learning model—and, by extension, the overall project. Its purpose is to confirm that the data is appropriately structured, consistent, and of sufficient quality to support reliable modeling.
 While every dataset and project is unique, applying a consistent EDA approach helps reduce the laborious and time-consuming nature of data preparation. A structured process enables quicker identification of data issues, improves understanding of key variables and relationships, and creates a more stable foundation for subsequent modeling decisions. </t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Feature Engineering</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Process of creating new input variables that better represent the underlying patterns in the data. It may include transformations (log, scaling), aggregations, interactions, temporal features, or domain-specific encodings. Effective feature engineering can significantly improve model performance even with simple algorithms. It embeds domain knowledge into the model and often provides more value than algorithmic complexity.  It is often one of the most impactful steps in the machine learning workflow.</t>
-        </is>
-      </c>
-    </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
@@ -697,56 +697,60 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>Feature Engineering</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Process of creating new input variables that better represent the underlying patterns in the data. It may include transformations (log, scaling), aggregations, interactions, temporal features, or domain-specific encodings. Effective feature engineering can significantly improve model performance even with simple algorithms. It embeds domain knowledge into the model and often provides more value than algorithmic complexity.  It is often one of the most impactful steps in the machine learning workflow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Feature Engineering</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Function creates derived variables, metrics, flags, or analytical features</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Process of identifying and retaining the most relevant variables for model training while removing redundant, noisy, or irrelevant features. This helps reduce overfitting, improve model performance, and increase interpretability. Feature selection techniques may be statistical, model-based, or embedded within the learning algorithm. The goal is to create a simpler, more robust feature set that generalizes well to new data.
 It is important to be in a position to Logically and Mathematically be in a position to defend inclusion and exclusion decisions. Although a highly technical step, it is critically important that stakeholders and partners are included and in references and terms which are appropriate for them.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Model Selection</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
-        </is>
-      </c>
-    </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -760,14 +764,10 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hyperparameter Tuning</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
-        </is>
-      </c>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Model Evaluation</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
+          <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
         </is>
       </c>
     </row>
@@ -804,12 +804,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Hyperparameter Tuning</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
+          <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
         </is>
       </c>
     </row>
@@ -826,10 +826,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Model Interpretability</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Model Evaluation</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -844,12 +848,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
+          <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
         </is>
       </c>
     </row>
@@ -866,14 +870,10 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Monitoring</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
-        </is>
-      </c>
+          <t>Model Interpretability</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -888,19 +888,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bias, Fairness, and Ethics</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
+          <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -910,19 +910,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Baseline Metrics (Current State)</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
+          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -932,12 +932,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Current State Analysis</t>
+          <t>Bias, Fairness, and Ethics</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
+          <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
         </is>
       </c>
     </row>
@@ -954,12 +954,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Desired State Metrics</t>
+          <t>Baseline Metrics (Current State)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
+          <t>Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
         </is>
       </c>
     </row>
@@ -976,12 +976,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Historical Overview</t>
+          <t>Current State Analysis</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
+          <t>Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
         </is>
       </c>
     </row>
@@ -998,19 +998,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Root Cause Assessment</t>
+          <t>Desired State Metrics</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
+          <t>Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1020,19 +1020,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Historical Overview</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
+          <t>Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Root Cause Assessment</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
+          <t>Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Desired State Metrics: Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
+          <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Current State Analysis: Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
+          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Root Cause Assessment: Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
+          <t>Desired State Metrics: Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Historical Overview: Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
+          <t>Current State Analysis: Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Baseline Metrics (Current State): Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
+          <t>Root Cause Assessment: Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
         </is>
       </c>
     </row>
@@ -1174,10 +1174,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Current State Assessment</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Historical Overview: Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1192,52 +1196,56 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Baseline Metrics (Current State): Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Current State Assessment</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>Data Collection</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Data collection involves identifying, sourcing, and acquiring the datasets required to solve the defined problem. This may include internal databases, APIs, logs, third-party data, or manually collected data. Key considerations include data availability, coverage, granularity, freshness, and legal or privacy constraints. The quality and relevance of collected data fundamentally limit the ceiling of model performance.
 Need to understand the data available to solve a problem, insure that it's documented, understood and trusted. Need to identify, not only information which is available, but information which is not available and should be.  This should be explicitly documented, referenced constantly and readily available (Semantic and Functional Definition).</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Root Cause Analysis</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Research and Exploration</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-    </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
@@ -1251,7 +1259,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Option Generation</t>
+          <t>Root Cause Analysis</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1269,7 +1277,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Solution Design</t>
+          <t>Research and Exploration</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1287,7 +1295,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Feasibility Assessment</t>
+          <t>Option Generation</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -1305,7 +1313,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Prioritization and Decision Making</t>
+          <t>Solution Design</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1323,7 +1331,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Implementation Planning</t>
+          <t>Feasibility Assessment</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1341,7 +1349,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Prioritization and Decision Making</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1359,7 +1367,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Testing and Validation</t>
+          <t>Implementation Planning</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1377,7 +1385,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Evaluation</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1395,7 +1403,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Optimization</t>
+          <t>Testing and Validation</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -1413,7 +1421,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Documentation and Knowledge Sharing</t>
+          <t>Evaluation</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -1431,14 +1439,10 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Monitoring</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
-        </is>
-      </c>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1453,7 +1457,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Continuous Improvement</t>
+          <t>Documentation and Knowledge Sharing</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -1471,10 +1475,50 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Continuous Improvement</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
           <t>Governance, Risk, and Ethics</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Streamlit/Data/defined_processes.xlsx
+++ b/Streamlit/Data/defined_processes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -764,10 +764,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Model Selection</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Feature Selection</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Methods that identify and retain a subset of existing features based on their relevance, importance, or contribution to a learning task. The goal is to reduce model complexity, improve generalization, and enhance interpretability without creating new features or altering their definitions. Feature selection techniques are typically applied as preprocessing or model-selection steps and often rely on statistical criteria or model-based importance measures.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -782,14 +786,10 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
-        </is>
-      </c>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hyperparameter Tuning</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
+          <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Model Evaluation</t>
+          <t>Hyperparameter Tuning</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
+          <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Model Evaluation</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
+          <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
         </is>
       </c>
     </row>
@@ -870,10 +870,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Model Interpretability</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -888,14 +892,10 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Deployment</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
-        </is>
-      </c>
+          <t>Model Interpretability</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -910,12 +910,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
+          <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
         </is>
       </c>
     </row>
@@ -932,19 +932,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bias, Fairness, and Ethics</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
+          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -954,12 +954,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Baseline Metrics (Current State)</t>
+          <t>Bias, Fairness, and Ethics</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
+          <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
         </is>
       </c>
     </row>
@@ -976,12 +976,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Current State Analysis</t>
+          <t>Baseline Metrics (Current State)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
+          <t>Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Desired State Metrics</t>
+          <t>Current State Analysis</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
+          <t>Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Historical Overview</t>
+          <t>Desired State Metrics</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
+          <t>Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
         </is>
       </c>
     </row>
@@ -1042,19 +1042,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Root Cause Assessment</t>
+          <t>Historical Overview</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
+          <t>Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1064,12 +1064,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Root Cause Assessment</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
+          <t>Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
         </is>
       </c>
     </row>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
+          <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Desired State Metrics: Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
+          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Current State Analysis: Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
+          <t>Desired State Metrics: Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Root Cause Assessment: Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
+          <t>Current State Analysis: Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Historical Overview: Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
+          <t>Root Cause Assessment: Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Baseline Metrics (Current State): Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
+          <t>Historical Overview: Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
         </is>
       </c>
     </row>
@@ -1218,10 +1218,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Current State Assessment</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Baseline Metrics (Current State): Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1236,34 +1240,34 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t>Current State Assessment</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>Data Collection</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>Data collection involves identifying, sourcing, and acquiring the datasets required to solve the defined problem. This may include internal databases, APIs, logs, third-party data, or manually collected data. Key considerations include data availability, coverage, granularity, freshness, and legal or privacy constraints. The quality and relevance of collected data fundamentally limit the ceiling of model performance.
 Need to understand the data available to solve a problem, insure that it's documented, understood and trusted. Need to identify, not only information which is available, but information which is not available and should be.  This should be explicitly documented, referenced constantly and readily available (Semantic and Functional Definition).</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Root Cause Analysis</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-    </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
@@ -1277,7 +1281,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Research and Exploration</t>
+          <t>Root Cause Analysis</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1295,7 +1299,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Option Generation</t>
+          <t>Research and Exploration</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -1313,7 +1317,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Solution Design</t>
+          <t>Option Generation</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1331,7 +1335,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Feasibility Assessment</t>
+          <t>Solution Design</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1349,7 +1353,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Prioritization and Decision Making</t>
+          <t>Feasibility Assessment</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1367,7 +1371,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Implementation Planning</t>
+          <t>Prioritization and Decision Making</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1385,7 +1389,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Implementation Planning</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1403,7 +1407,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Testing and Validation</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -1421,7 +1425,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Evaluation</t>
+          <t>Testing and Validation</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -1439,7 +1443,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Optimization</t>
+          <t>Evaluation</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -1457,7 +1461,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Documentation and Knowledge Sharing</t>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -1475,14 +1479,10 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Monitoring</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
-        </is>
-      </c>
+          <t>Documentation and Knowledge Sharing</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1497,10 +1497,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Continuous Improvement</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1515,10 +1519,28 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
+          <t>Continuous Improvement</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
           <t>Governance, Risk, and Ethics</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Streamlit/Data/defined_processes.xlsx
+++ b/Streamlit/Data/defined_processes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Feature Selection</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -451,19 +451,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Consideration</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
+          <t>Avoid ambiguous features. Is a Banana ripe, who says so?</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Feature Selection</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -473,19 +473,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Consideration</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
+          <t>Careful when something is truly random generated, Atmospheric Change, Earthquakes, Stocks. Very difficult, if not impossible to predict.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Feature Selection</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -495,19 +495,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Consideration</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Desired State Metrics: Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
+          <t>How robust is your model to change and what is it actually predict. 
+MNIST performance when tilting Images, of adding noise.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Feature Selection</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -517,19 +518,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Current State Analysis: Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
+          <t>Generate feature importance or explanation outputs. Helps understand what drives model predictions.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Feature Selection</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -539,19 +540,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Root Cause Assessment: Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
+          <t>Remove features with high missingness or low variance. Reduces noise and improves model stability.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Feature Selection</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -561,19 +562,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Historical Overview: Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
+          <t>Check for multicollinearity or redundant features. Helps prevent unstable models and improves interpretability.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Feature Selection</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -583,12 +584,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Baseline Metrics (Current State): Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
+          <t>Validate selected features using model or statistical methods. Ensures the retained features actually contribute to predictive performance.</t>
         </is>
       </c>
     </row>
@@ -605,33 +606,187 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>Goal Setting</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Desired State Metrics: Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Current State Analysis: Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Root Cause Assessment: Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Historical Overview: Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Baseline Metrics (Current State): Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>Data Collection</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Data collection involves identifying, sourcing, and acquiring the datasets required to solve the defined problem. This may include internal databases, APIs, logs, third-party data, or manually collected data. Key considerations include data availability, coverage, granularity, freshness, and legal or privacy constraints. The quality and relevance of collected data fundamentally limit the ceiling of model performance.
 Need to understand the data available to solve a problem, insure that it's documented, understood and trusted. Need to identify, not only information which is available, but information which is not available and should be.  This should be explicitly documented, referenced constantly and readily available (Semantic and Functional Definition).</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>Data Preparation</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Data preparation focuses on cleaning and structuring raw data into a usable format for modeling. This includes handling missing values, correcting errors, standardizing formats, encoding categorical variables, and aligning labels with features. It also often involves train/validation/test splitting to prevent data leakage. This step is critical because most models assume clean, well-structured inputs and are highly sensitive to data issues.
 Need to establish up a consistent, robust and repeatable data ingestion process, which starts at the outset of the project. Where the infrastructure is not immediately available, need to clearly document the journey.  Need to call out requirements, expectations and limitations, and where resources are necessary, they should be identified at this point. 
@@ -639,264 +794,118 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>Data Preparation</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t xml:space="preserve">   Function cleans, reshapes, filters, joins, or transforms data into usable form.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Exploratory Data Analysis</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t xml:space="preserve">Foundational step in ensuring the success of a machine learning model—and, by extension, the overall project. Its purpose is to confirm that the data is appropriately structured, consistent, and of sufficient quality to support reliable modeling.
 While every dataset and project is unique, applying a consistent EDA approach helps reduce the laborious and time-consuming nature of data preparation. A structured process enables quicker identification of data issues, improves understanding of key variables and relationships, and creates a more stable foundation for subsequent modeling decisions. </t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>Feature Engineering</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Process of creating new input variables that better represent the underlying patterns in the data. It may include transformations (log, scaling), aggregations, interactions, temporal features, or domain-specific encodings. Effective feature engineering can significantly improve model performance even with simple algorithms. It embeds domain knowledge into the model and often provides more value than algorithmic complexity.  It is often one of the most impactful steps in the machine learning workflow.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>Feature Engineering</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t xml:space="preserve">   Function creates derived variables, metrics, flags, or analytical features</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Process of identifying and retaining the most relevant variables for model training while removing redundant, noisy, or irrelevant features. This helps reduce overfitting, improve model performance, and increase interpretability. Feature selection techniques may be statistical, model-based, or embedded within the learning algorithm. The goal is to create a simpler, more robust feature set that generalizes well to new data.
 It is important to be in a position to Logically and Mathematically be in a position to defend inclusion and exclusion decisions. Although a highly technical step, it is critically important that stakeholders and partners are included and in references and terms which are appropriate for them.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Feature Selection</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Methods that identify and retain a subset of existing features based on their relevance, importance, or contribution to a learning task. The goal is to reduce model complexity, improve generalization, and enhance interpretability without creating new features or altering their definitions. Feature selection techniques are typically applied as preprocessing or model-selection steps and often rely on statistical criteria or model-based importance measures.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Model Selection</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Hyperparameter Tuning</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Model Evaluation</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Validation</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Model Interpretability</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-    </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
@@ -910,12 +919,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Feature Selection</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
+          <t>Requirement: Generate feature importance or explanation outputs. Helps understand what drives model predictions.</t>
         </is>
       </c>
     </row>
@@ -932,12 +941,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Feature Selection</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
+          <t>Requirement: Remove features with high missingness or low variance. Reduces noise and improves model stability.</t>
         </is>
       </c>
     </row>
@@ -954,19 +963,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bias, Fairness, and Ethics</t>
+          <t>Feature Selection</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
+          <t>Requirement: Check for multicollinearity or redundant features. Helps prevent unstable models and improves interpretability.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -976,19 +985,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Baseline Metrics (Current State)</t>
+          <t>Feature Selection</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
+          <t>Requirement: Validate selected features using model or statistical methods. Ensures the retained features actually contribute to predictive performance.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -998,19 +1007,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Current State Analysis</t>
+          <t>Feature Selection</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
+          <t>Consideration: Avoid ambiguous features. Is a Banana ripe, who says so?</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1020,19 +1029,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Desired State Metrics</t>
+          <t>Feature Selection</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
+          <t>Consideration: Careful when something is truly random generated, Atmospheric Change, Earthquakes, Stocks. Very difficult, if not impossible to predict.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1042,19 +1051,20 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Historical Overview</t>
+          <t>Feature Selection</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
+          <t>Consideration: How robust is your model to change and what is it actually predict. 
+MNIST performance when tilting Images, of adding noise.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1064,19 +1074,15 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Root Cause Assessment</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
-        </is>
-      </c>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1086,19 +1092,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
+          <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1108,19 +1114,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Hyperparameter Tuning</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
+          <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1130,19 +1136,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Model Evaluation</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Desired State Metrics: Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
+          <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1152,19 +1158,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Current State Analysis: Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
+          <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1174,19 +1180,15 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Root Cause Assessment: Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
-        </is>
-      </c>
+          <t>Model Interpretability</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1196,19 +1198,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Historical Overview: Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
+          <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1218,19 +1220,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Baseline Metrics (Current State): Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
+          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1240,15 +1242,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Current State Assessment</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>Bias, Fairness, and Ethics</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1258,254 +1264,298 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
+          <t>Baseline Metrics (Current State)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Current State Analysis</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Desired State Metrics</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Historical Overview</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Root Cause Assessment</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Goal Setting</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Desired State Metrics: Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Current State Analysis: Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Root Cause Assessment: Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Historical Overview: Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Baseline Metrics (Current State): Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Current State Assessment</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
           <t>Data Collection</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Data collection involves identifying, sourcing, and acquiring the datasets required to solve the defined problem. This may include internal databases, APIs, logs, third-party data, or manually collected data. Key considerations include data availability, coverage, granularity, freshness, and legal or privacy constraints. The quality and relevance of collected data fundamentally limit the ceiling of model performance.
 Need to understand the data available to solve a problem, insure that it's documented, understood and trusted. Need to identify, not only information which is available, but information which is not available and should be.  This should be explicitly documented, referenced constantly and readily available (Semantic and Functional Definition).</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Root Cause Analysis</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Research and Exploration</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Option Generation</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Solution Design</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Feasibility Assessment</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Prioritization and Decision Making</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Implementation Planning</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Execution</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Testing and Validation</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Evaluation</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Optimization</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Documentation and Knowledge Sharing</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Monitoring</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
-        </is>
-      </c>
-    </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
@@ -1519,7 +1569,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Continuous Improvement</t>
+          <t>Root Cause Analysis</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -1537,10 +1587,248 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
+          <t>Research and Exploration</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Option Generation</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Solution Design</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Feasibility Assessment</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Prioritization and Decision Making</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Implementation Planning</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Execution</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Testing and Validation</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Evaluation</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Documentation and Knowledge Sharing</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Continuous Improvement</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
           <t>Governance, Risk, and Ethics</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Streamlit/Data/defined_processes.xlsx
+++ b/Streamlit/Data/defined_processes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -606,12 +606,13 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Exploratory Data Analysis</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
+          <t xml:space="preserve">Foundational step in ensuring the success of a machine learning model—and, by extension, the overall project. Its purpose is to confirm that the data is appropriately structured, consistent, and of sufficient quality to support reliable modeling.
+While every dataset and project is unique, applying a consistent EDA approach helps reduce the laborious and time-consuming nature of data preparation. A structured process enables quicker identification of data issues, improves understanding of key variables and relationships, and creates a more stable foundation for subsequent modeling decisions. </t>
         </is>
       </c>
     </row>
@@ -628,14 +629,10 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
-        </is>
-      </c>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -650,12 +647,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Desired State Metrics: Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
+          <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
         </is>
       </c>
     </row>
@@ -672,12 +669,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Hyperparameter Tuning</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Current State Analysis: Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
+          <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
         </is>
       </c>
     </row>
@@ -694,12 +691,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Root Cause Assessment: Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
+          <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
         </is>
       </c>
     </row>
@@ -716,14 +713,10 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Historical Overview: Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
-        </is>
-      </c>
+          <t>Model Interpretability</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -738,12 +731,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Baseline Metrics (Current State): Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
+          <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
         </is>
       </c>
     </row>
@@ -760,13 +753,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Data Collection</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Data collection involves identifying, sourcing, and acquiring the datasets required to solve the defined problem. This may include internal databases, APIs, logs, third-party data, or manually collected data. Key considerations include data availability, coverage, granularity, freshness, and legal or privacy constraints. The quality and relevance of collected data fundamentally limit the ceiling of model performance.
-Need to understand the data available to solve a problem, insure that it's documented, understood and trusted. Need to identify, not only information which is available, but information which is not available and should be.  This should be explicitly documented, referenced constantly and readily available (Semantic and Functional Definition).</t>
+          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
         </is>
       </c>
     </row>
@@ -783,21 +775,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Data Preparation</t>
+          <t>Bias, Fairness, and Ethics</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Data preparation focuses on cleaning and structuring raw data into a usable format for modeling. This includes handling missing values, correcting errors, standardizing formats, encoding categorical variables, and aligning labels with features. It also often involves train/validation/test splitting to prevent data leakage. This step is critical because most models assume clean, well-structured inputs and are highly sensitive to data issues.
-Need to establish up a consistent, robust and repeatable data ingestion process, which starts at the outset of the project. Where the infrastructure is not immediately available, need to clearly document the journey.  Need to call out requirements, expectations and limitations, and where resources are necessary, they should be identified at this point. 
-Where operational changes are necessary, or a prerequisite, need to understand how these will documented and escalated or addressed.</t>
+          <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -807,19 +797,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Data Preparation</t>
+          <t>Baseline Metrics (Current State)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Function cleans, reshapes, filters, joins, or transforms data into usable form.</t>
+          <t>Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -829,20 +819,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Exploratory Data Analysis</t>
+          <t>Current State Analysis</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Foundational step in ensuring the success of a machine learning model—and, by extension, the overall project. Its purpose is to confirm that the data is appropriately structured, consistent, and of sufficient quality to support reliable modeling.
-While every dataset and project is unique, applying a consistent EDA approach helps reduce the laborious and time-consuming nature of data preparation. A structured process enables quicker identification of data issues, improves understanding of key variables and relationships, and creates a more stable foundation for subsequent modeling decisions. </t>
+          <t>Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -852,19 +841,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Feature Engineering</t>
+          <t>Desired State Metrics</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Process of creating new input variables that better represent the underlying patterns in the data. It may include transformations (log, scaling), aggregations, interactions, temporal features, or domain-specific encodings. Effective feature engineering can significantly improve model performance even with simple algorithms. It embeds domain knowledge into the model and often provides more value than algorithmic complexity.  It is often one of the most impactful steps in the machine learning workflow.</t>
+          <t>Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -874,19 +863,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Feature Engineering</t>
+          <t>Historical Overview</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Function creates derived variables, metrics, flags, or analytical features</t>
+          <t>Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -896,20 +885,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Feature Selection</t>
+          <t>Root Cause Assessment</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Process of identifying and retaining the most relevant variables for model training while removing redundant, noisy, or irrelevant features. This helps reduce overfitting, improve model performance, and increase interpretability. Feature selection techniques may be statistical, model-based, or embedded within the learning algorithm. The goal is to create a simpler, more robust feature set that generalizes well to new data.
-It is important to be in a position to Logically and Mathematically be in a position to defend inclusion and exclusion decisions. Although a highly technical step, it is critically important that stakeholders and partners are included and in references and terms which are appropriate for them.</t>
+          <t>Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -919,19 +907,15 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Feature Selection</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Requirement: Generate feature importance or explanation outputs. Helps understand what drives model predictions.</t>
-        </is>
-      </c>
+          <t>Current State Assessment</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -941,19 +925,15 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Feature Selection</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Requirement: Remove features with high missingness or low variance. Reduces noise and improves model stability.</t>
-        </is>
-      </c>
+          <t>Root Cause Analysis</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -963,19 +943,15 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Feature Selection</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Requirement: Check for multicollinearity or redundant features. Helps prevent unstable models and improves interpretability.</t>
-        </is>
-      </c>
+          <t>Research and Exploration</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -985,19 +961,15 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Feature Selection</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Requirement: Validate selected features using model or statistical methods. Ensures the retained features actually contribute to predictive performance.</t>
-        </is>
-      </c>
+          <t>Option Generation</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1007,19 +979,15 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Feature Selection</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Consideration: Avoid ambiguous features. Is a Banana ripe, who says so?</t>
-        </is>
-      </c>
+          <t>Solution Design</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1029,19 +997,15 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Feature Selection</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Consideration: Careful when something is truly random generated, Atmospheric Change, Earthquakes, Stocks. Very difficult, if not impossible to predict.</t>
-        </is>
-      </c>
+          <t>Feasibility Assessment</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1051,20 +1015,15 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Feature Selection</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Consideration: How robust is your model to change and what is it actually predict. 
-MNIST performance when tilting Images, of adding noise.</t>
-        </is>
-      </c>
+          <t>Prioritization and Decision Making</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1074,7 +1033,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Model Selection</t>
+          <t>Implementation Planning</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1082,7 +1041,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1092,19 +1051,15 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
-        </is>
-      </c>
+          <t>Execution</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1114,19 +1069,15 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hyperparameter Tuning</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
-        </is>
-      </c>
+          <t>Testing and Validation</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1136,19 +1087,15 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Model Evaluation</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
-        </is>
-      </c>
+          <t>Evaluation</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1158,19 +1105,15 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Validation</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
-        </is>
-      </c>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1180,7 +1123,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Model Interpretability</t>
+          <t>Documentation and Knowledge Sharing</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1188,7 +1131,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1198,19 +1141,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
+          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1220,19 +1163,15 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Monitoring</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
-        </is>
-      </c>
+          <t>Continuous Improvement</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1242,593 +1181,10 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bias, Fairness, and Ethics</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Problem Definition</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Baseline Metrics (Current State)</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Problem Definition</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Current State Analysis</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Problem Definition</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Desired State Metrics</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Problem Definition</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Historical Overview</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Problem Definition</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Root Cause Assessment</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Goal Setting</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Problem Definition</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Problem Definition</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Desired State Metrics: Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Problem Definition</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Current State Analysis: Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Problem Definition</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Root Cause Assessment: Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Problem Definition</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Historical Overview: Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Problem Definition</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Baseline Metrics (Current State): Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Current State Assessment</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Data Collection</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Data collection involves identifying, sourcing, and acquiring the datasets required to solve the defined problem. This may include internal databases, APIs, logs, third-party data, or manually collected data. Key considerations include data availability, coverage, granularity, freshness, and legal or privacy constraints. The quality and relevance of collected data fundamentally limit the ceiling of model performance.
-Need to understand the data available to solve a problem, insure that it's documented, understood and trusted. Need to identify, not only information which is available, but information which is not available and should be.  This should be explicitly documented, referenced constantly and readily available (Semantic and Functional Definition).</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Root Cause Analysis</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Research and Exploration</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Option Generation</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Solution Design</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Feasibility Assessment</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Prioritization and Decision Making</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Implementation Planning</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Execution</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Testing and Validation</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Evaluation</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Optimization</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Documentation and Knowledge Sharing</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Monitoring</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Continuous Improvement</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
           <t>Governance, Risk, and Ethics</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Streamlit/Data/defined_processes.xlsx
+++ b/Streamlit/Data/defined_processes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Feature Selection</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -451,19 +451,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Consideration</t>
+          <t>Exploratory Data Analysis</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Avoid ambiguous features. Is a Banana ripe, who says so?</t>
+          <t xml:space="preserve">Foundational step in ensuring the success of a machine learning model—and, by extension, the overall project. Its purpose is to confirm that the data is appropriately structured, consistent, and of sufficient quality to support reliable modeling.
+While every dataset and project is unique, applying a consistent EDA approach helps reduce the laborious and time-consuming nature of data preparation. A structured process enables quicker identification of data issues, improves understanding of key variables and relationships, and creates a more stable foundation for subsequent modeling decisions. </t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Feature Selection</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -473,19 +474,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Consideration</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Careful when something is truly random generated, Atmospheric Change, Earthquakes, Stocks. Very difficult, if not impossible to predict.</t>
+          <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Feature Selection</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -495,20 +496,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Consideration</t>
+          <t>Baseline Metrics (Current State)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>How robust is your model to change and what is it actually predict. 
-MNIST performance when tilting Images, of adding noise.</t>
+          <t>Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Feature Selection</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -518,19 +518,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Requirement</t>
+          <t>Current State Analysis</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Generate feature importance or explanation outputs. Helps understand what drives model predictions.</t>
+          <t>Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Feature Selection</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -540,19 +540,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Requirement</t>
+          <t>Desired State Metrics</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Remove features with high missingness or low variance. Reduces noise and improves model stability.</t>
+          <t>Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Feature Selection</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -562,19 +562,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Requirement</t>
+          <t>Historical Overview</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Check for multicollinearity or redundant features. Helps prevent unstable models and improves interpretability.</t>
+          <t>Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Feature Selection</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -584,19 +584,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Requirement</t>
+          <t>Root Cause Assessment</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Validate selected features using model or statistical methods. Ensures the retained features actually contribute to predictive performance.</t>
+          <t>Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -606,20 +606,15 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Exploratory Data Analysis</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Foundational step in ensuring the success of a machine learning model—and, by extension, the overall project. Its purpose is to confirm that the data is appropriately structured, consistent, and of sufficient quality to support reliable modeling.
-While every dataset and project is unique, applying a consistent EDA approach helps reduce the laborious and time-consuming nature of data preparation. A structured process enables quicker identification of data issues, improves understanding of key variables and relationships, and creates a more stable foundation for subsequent modeling decisions. </t>
-        </is>
-      </c>
+          <t>Current State Assessment</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -629,7 +624,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Model Selection</t>
+          <t>Root Cause Analysis</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -637,7 +632,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -647,19 +642,15 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
-        </is>
-      </c>
+          <t>Research and Exploration</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -669,19 +660,15 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hyperparameter Tuning</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
-        </is>
-      </c>
+          <t>Option Generation</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -691,19 +678,15 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Validation</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
-        </is>
-      </c>
+          <t>Solution Design</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -713,7 +696,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Model Interpretability</t>
+          <t>Feasibility Assessment</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -721,7 +704,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -731,19 +714,15 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Deployment</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
-        </is>
-      </c>
+          <t>Prioritization and Decision Making</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -753,19 +732,15 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Monitoring</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
-        </is>
-      </c>
+          <t>Implementation Planning</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -775,19 +750,15 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bias, Fairness, and Ethics</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
-        </is>
-      </c>
+          <t>Execution</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -797,19 +768,15 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Baseline Metrics (Current State)</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
-        </is>
-      </c>
+          <t>Testing and Validation</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -819,19 +786,15 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Current State Analysis</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
-        </is>
-      </c>
+          <t>Evaluation</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -841,19 +804,15 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Desired State Metrics</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
-        </is>
-      </c>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -863,19 +822,15 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Historical Overview</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
-        </is>
-      </c>
+          <t>Documentation and Knowledge Sharing</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -885,14 +840,10 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Root Cause Assessment</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
-        </is>
-      </c>
+          <t>Continuous Improvement</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -907,284 +858,10 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Current State Assessment</t>
+          <t>Governance, Risk, and Ethics</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Root Cause Analysis</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Research and Exploration</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Option Generation</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Solution Design</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Feasibility Assessment</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Prioritization and Decision Making</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Implementation Planning</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Execution</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Testing and Validation</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Evaluation</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Optimization</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Documentation and Knowledge Sharing</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Monitoring</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Continuous Improvement</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Governance, Risk, and Ethics</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Streamlit/Data/defined_processes.xlsx
+++ b/Streamlit/Data/defined_processes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,108 +451,111 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Goal Setting</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Data Collection</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Data collection involves identifying, sourcing, and acquiring the datasets required to solve the defined problem. This may include internal databases, APIs, logs, third-party data, or manually collected data. Key considerations include data availability, coverage, granularity, freshness, and legal or privacy constraints. The quality and relevance of collected data fundamentally limit the ceiling of model performance.
+Need to understand the data available to solve a problem, insure that it's documented, understood and trusted. Need to identify, not only information which is available, but information which is not available and should be.  This should be explicitly documented, referenced constantly and readily available (Semantic and Functional Definition).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Data Preparation</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Data preparation focuses on cleaning and structuring raw data into a usable format for modeling. This includes handling missing values, correcting errors, standardizing formats, encoding categorical variables, and aligning labels with features. It also often involves train/validation/test splitting to prevent data leakage. This step is critical because most models assume clean, well-structured inputs and are highly sensitive to data issues.
+Need to establish up a consistent, robust and repeatable data ingestion process, which starts at the outset of the project. Where the infrastructure is not immediately available, need to clearly document the journey.  Need to call out requirements, expectations and limitations, and where resources are necessary, they should be identified at this point. 
+Where operational changes are necessary, or a prerequisite, need to understand how these will documented and escalated or addressed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>Exploratory Data Analysis</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">Foundational step in ensuring the success of a machine learning model—and, by extension, the overall project. Its purpose is to confirm that the data is appropriately structured, consistent, and of sufficient quality to support reliable modeling.
 While every dataset and project is unique, applying a consistent EDA approach helps reduce the laborious and time-consuming nature of data preparation. A structured process enables quicker identification of data issues, improves understanding of key variables and relationships, and creates a more stable foundation for subsequent modeling decisions. </t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Validation</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Problem Definition</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Baseline Metrics (Current State)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Problem Definition</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Current State Analysis</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Problem Definition</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Desired State Metrics</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
-        </is>
-      </c>
-    </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -562,19 +565,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Historical Overview</t>
+          <t>Feature Engineering</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
+          <t>Process of creating new input variables that better represent the underlying patterns in the data. It may include transformations (log, scaling), aggregations, interactions, temporal features, or domain-specific encodings. Effective feature engineering can significantly improve model performance even with simple algorithms. It embeds domain knowledge into the model and often provides more value than algorithmic complexity.  It is often one of the most impactful steps in the machine learning workflow.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -584,19 +587,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Root Cause Assessment</t>
+          <t>Feature Selection</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
+          <t>Process of identifying and retaining the most relevant variables for model training while removing redundant, noisy, or irrelevant features. This helps reduce overfitting, improve model performance, and increase interpretability. Feature selection techniques may be statistical, model-based, or embedded within the learning algorithm. The goal is to create a simpler, more robust feature set that generalizes well to new data.
+It is important to be in a position to Logically and Mathematically be in a position to defend inclusion and exclusion decisions. Although a highly technical step, it is critically important that stakeholders and partners are included and in references and terms which are appropriate for them.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -606,7 +610,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Current State Assessment</t>
+          <t>Model Selection</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -614,7 +618,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -624,15 +628,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Root Cause Analysis</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -642,15 +650,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Research and Exploration</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Hyperparameter Tuning</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -660,15 +672,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Option Generation</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Model Evaluation</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -678,15 +694,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Solution Design</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -696,7 +716,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Feasibility Assessment</t>
+          <t>Model Interpretability</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -704,7 +724,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -714,15 +734,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Prioritization and Decision Making</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Deployment</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -732,15 +756,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Implementation Planning</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -750,15 +778,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Execution</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Bias, Fairness, and Ethics</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Presentation Tenants</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -768,7 +800,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Testing and Validation</t>
+          <t>Cardinal Presentation Sins</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -776,7 +808,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Presentation Tenants</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -786,7 +818,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Evaluation</t>
+          <t>Make it as Short as Possible</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -794,7 +826,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Presentation Tenants</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -804,7 +836,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Optimization</t>
+          <t>Re-enforce the Message</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -812,7 +844,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Presentation Tenants</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -822,7 +854,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Documentation and Knowledge Sharing</t>
+          <t>Understand Your Audience</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -830,7 +862,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Presentation Tenants</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -840,7 +872,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Continuous Improvement</t>
+          <t>Understand Your Message</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -848,7 +880,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Presentation Tenants</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -858,10 +890,605 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>Understand Your Visuals</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Baseline Metrics (Current State)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Current State Analysis</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Desired State Metrics</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Historical Overview</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Root Cause Assessment</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Goal Setting</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Current State Assessment</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Data Collection</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Data collection involves identifying, sourcing, and acquiring the datasets required to solve the defined problem. This may include internal databases, APIs, logs, third-party data, or manually collected data. Key considerations include data availability, coverage, granularity, freshness, and legal or privacy constraints. The quality and relevance of collected data fundamentally limit the ceiling of model performance.
+Need to understand the data available to solve a problem, insure that it's documented, understood and trusted. Need to identify, not only information which is available, but information which is not available and should be.  This should be explicitly documented, referenced constantly and readily available (Semantic and Functional Definition).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Root Cause Analysis</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Research and Exploration</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Option Generation</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Solution Design</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Feasibility Assessment</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Prioritization and Decision Making</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Implementation Planning</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Execution</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Testing and Validation</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Evaluation</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Documentation and Knowledge Sharing</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Continuous Improvement</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
           <t>Governance, Risk, and Ethics</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Story Telling Tenants</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>And Because of this..</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Story Telling Tenants</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>And Because of this....</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Story Telling Tenants</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>And Ever Since that Day.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Story Telling Tenants</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>And Every Day</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Story Telling Tenants</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Once Upon a Time</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Story Telling Tenants</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Until Finally</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Story Telling Tenants</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Until One Day</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Streamlit/Data/defined_processes.xlsx
+++ b/Streamlit/Data/defined_processes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Decision Making</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -451,19 +451,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Identify Criteria</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
+          <t>Always identify multiple criteria, how can we fairly compare approaches.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Decision Making</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -473,55 +473,109 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
-        </is>
-      </c>
+          <t>Identify Evaluation Framework</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Decision Making</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Machine Learning Lifecycle</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Goal Setting</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>Data Collection</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Data collection involves identifying, sourcing, and acquiring the datasets required to solve the defined problem. This may include internal databases, APIs, logs, third-party data, or manually collected data. Key considerations include data availability, coverage, granularity, freshness, and legal or privacy constraints. The quality and relevance of collected data fundamentally limit the ceiling of model performance.
 Need to understand the data available to solve a problem, insure that it's documented, understood and trusted. Need to identify, not only information which is available, but information which is not available and should be.  This should be explicitly documented, referenced constantly and readily available (Semantic and Functional Definition).</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Machine Learning Lifecycle</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>Data Preparation</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Data preparation focuses on cleaning and structuring raw data into a usable format for modeling. This includes handling missing values, correcting errors, standardizing formats, encoding categorical variables, and aligning labels with features. It also often involves train/validation/test splitting to prevent data leakage. This step is critical because most models assume clean, well-structured inputs and are highly sensitive to data issues.
 Need to establish up a consistent, robust and repeatable data ingestion process, which starts at the outset of the project. Where the infrastructure is not immediately available, need to clearly document the journey.  Need to call out requirements, expectations and limitations, and where resources are necessary, they should be identified at this point. 
@@ -529,136 +583,74 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Machine Learning Lifecycle</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>Exploratory Data Analysis</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">Foundational step in ensuring the success of a machine learning model—and, by extension, the overall project. Its purpose is to confirm that the data is appropriately structured, consistent, and of sufficient quality to support reliable modeling.
 While every dataset and project is unique, applying a consistent EDA approach helps reduce the laborious and time-consuming nature of data preparation. A structured process enables quicker identification of data issues, improves understanding of key variables and relationships, and creates a more stable foundation for subsequent modeling decisions. </t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Machine Learning Lifecycle</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>Feature Engineering</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Process of creating new input variables that better represent the underlying patterns in the data. It may include transformations (log, scaling), aggregations, interactions, temporal features, or domain-specific encodings. Effective feature engineering can significantly improve model performance even with simple algorithms. It embeds domain knowledge into the model and often provides more value than algorithmic complexity.  It is often one of the most impactful steps in the machine learning workflow.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Machine Learning Lifecycle</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Process of identifying and retaining the most relevant variables for model training while removing redundant, noisy, or irrelevant features. This helps reduce overfitting, improve model performance, and increase interpretability. Feature selection techniques may be statistical, model-based, or embedded within the learning algorithm. The goal is to create a simpler, more robust feature set that generalizes well to new data.
 It is important to be in a position to Logically and Mathematically be in a position to defend inclusion and exclusion decisions. Although a highly technical step, it is critically important that stakeholders and partners are included and in references and terms which are appropriate for them.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Model Selection</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Hyperparameter Tuning</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
-        </is>
-      </c>
-    </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -672,14 +664,10 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Model Evaluation</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
-        </is>
-      </c>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -694,12 +682,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
+          <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
         </is>
       </c>
     </row>
@@ -716,10 +704,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Model Interpretability</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Hyperparameter Tuning</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -734,12 +726,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Model Evaluation</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
+          <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
         </is>
       </c>
     </row>
@@ -756,12 +748,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
+          <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
         </is>
       </c>
     </row>
@@ -778,19 +770,15 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bias, Fairness, and Ethics</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
-        </is>
-      </c>
+          <t>Model Interpretability</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Presentation Tenants</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -800,15 +788,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cardinal Presentation Sins</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Deployment</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Presentation Tenants</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -818,15 +810,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Make it as Short as Possible</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Presentation Tenants</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -836,10 +832,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Re-enforce the Message</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Bias, Fairness, and Ethics</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Understand Your Audience</t>
+          <t>Cardinal Presentation Sins</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -872,7 +872,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Understand Your Message</t>
+          <t>Make it as Short as Possible</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -890,7 +890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Understand Your Visuals</t>
+          <t>Re-enforce the Message</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -898,7 +898,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Presentation Tenants</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -908,19 +908,15 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Baseline Metrics (Current State)</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
-        </is>
-      </c>
+          <t>Understand Your Audience</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Presentation Tenants</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -930,19 +926,15 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Current State Analysis</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
-        </is>
-      </c>
+          <t>Understand Your Message</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Presentation Tenants</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -952,14 +944,10 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Desired State Metrics</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
-        </is>
-      </c>
+          <t>Understand Your Visuals</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -974,12 +962,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Historical Overview</t>
+          <t>Baseline Metrics (Current State)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
+          <t>Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
         </is>
       </c>
     </row>
@@ -996,19 +984,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Root Cause Assessment</t>
+          <t>Current State Analysis</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
+          <t>Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1018,19 +1006,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Desired State Metrics</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
+          <t>Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1040,19 +1028,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Historical Overview</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
+          <t>Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1062,10 +1050,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Current State Assessment</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>Root Cause Assessment</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1080,70 +1072,78 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>Goal Setting</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Current State Assessment</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
           <t>Data Collection</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>Data collection involves identifying, sourcing, and acquiring the datasets required to solve the defined problem. This may include internal databases, APIs, logs, third-party data, or manually collected data. Key considerations include data availability, coverage, granularity, freshness, and legal or privacy constraints. The quality and relevance of collected data fundamentally limit the ceiling of model performance.
 Need to understand the data available to solve a problem, insure that it's documented, understood and trusted. Need to identify, not only information which is available, but information which is not available and should be.  This should be explicitly documented, referenced constantly and readily available (Semantic and Functional Definition).</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Root Cause Analysis</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Research and Exploration</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Option Generation</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-    </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Solution Design</t>
+          <t>Root Cause Analysis</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Feasibility Assessment</t>
+          <t>Research and Exploration</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Prioritization and Decision Making</t>
+          <t>Option Generation</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Implementation Planning</t>
+          <t>Solution Design</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Feasibility Assessment</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Testing and Validation</t>
+          <t>Prioritization and Decision Making</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Evaluation</t>
+          <t>Implementation Planning</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Optimization</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Documentation and Knowledge Sharing</t>
+          <t>Testing and Validation</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1319,14 +1319,10 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Monitoring</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
-        </is>
-      </c>
+          <t>Evaluation</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1341,7 +1337,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Continuous Improvement</t>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1359,7 +1355,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Governance, Risk, and Ethics</t>
+          <t>Documentation and Knowledge Sharing</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -1367,7 +1363,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Story Telling Tenants</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1377,15 +1373,19 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>And Because of this..</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Story Telling Tenants</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>And Because of this....</t>
+          <t>Continuous Improvement</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -1403,7 +1403,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Story Telling Tenants</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>And Ever Since that Day.</t>
+          <t>Governance, Risk, and Ethics</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>And Every Day</t>
+          <t>And Because of this..</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Once Upon a Time</t>
+          <t>And Because of this....</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Until Finally</t>
+          <t>And Ever Since that Day.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -1485,10 +1485,64 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
+          <t>And Every Day</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Story Telling Tenants</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Once Upon a Time</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Story Telling Tenants</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Until Finally</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Story Telling Tenants</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
           <t>Until One Day</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Streamlit/Data/defined_processes.xlsx
+++ b/Streamlit/Data/defined_processes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,21 +437,6 @@
           <t>Definition</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>NP_ORDER</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>CAT_ORDER</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>PROC_ORDER</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -474,11 +459,6 @@
           <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -502,11 +482,6 @@
 Need to understand the data available to solve a problem, insure that it's documented, understood and trusted. Need to identify, not only information which is available, but information which is not available and should be.  This should be explicitly documented, referenced constantly and readily available (Semantic and Functional Definition).</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -531,11 +506,6 @@
 Where operational changes are necessary, or a prerequisite, need to understand how these will documented and escalated or addressed.</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -558,11 +528,6 @@
           <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -586,11 +551,6 @@
 While every dataset and project is unique, applying a consistent EDA approach helps reduce the laborious and time-consuming nature of data preparation. A structured process enables quicker identification of data issues, improves understanding of key variables and relationships, and creates a more stable foundation for subsequent modeling decisions. </t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -613,11 +573,6 @@
           <t>Process of creating new input variables that better represent the underlying patterns in the data. It may include transformations (log, scaling), aggregations, interactions, temporal features, or domain-specific encodings. Effective feature engineering can significantly improve model performance even with simple algorithms. It embeds domain knowledge into the model and often provides more value than algorithmic complexity.  It is often one of the most impactful steps in the machine learning workflow.</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -641,11 +596,6 @@
 It is important to be in a position to Logically and Mathematically be in a position to defend inclusion and exclusion decisions. Although a highly technical step, it is critically important that stakeholders and partners are included and in references and terms which are appropriate for them.</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -668,11 +618,6 @@
           <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -695,11 +640,6 @@
           <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -722,15 +662,6 @@
           <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>14</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -753,15 +684,6 @@
           <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>15</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -784,15 +706,6 @@
           <t>Data collection involves identifying, sourcing, and acquiring the datasets required to solve the defined problem. This may include internal databases, APIs, logs, third-party data, or manually collected data. Key considerations include data availability, coverage, granularity, freshness, and legal or privacy constraints. The quality and relevance of collected data fundamentally limit the ceiling of model performance.
 Need to understand the data available to solve a problem, insure that it's documented, understood and trusted. Need to identify, not only information which is available, but information which is not available and should be.  This should be explicitly documented, referenced constantly and readily available (Semantic and Functional Definition).</t>
         </is>
-      </c>
-      <c r="E13" t="n">
-        <v>16</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -818,15 +731,6 @@
 Where operational changes are necessary, or a prerequisite, need to understand how these will documented and escalated or addressed.</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>17</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="n">
-        <v>3</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -850,15 +754,6 @@
 While every dataset and project is unique, applying a consistent EDA approach helps reduce the laborious and time-consuming nature of data preparation. A structured process enables quicker identification of data issues, improves understanding of key variables and relationships, and creates a more stable foundation for subsequent modeling decisions. </t>
         </is>
       </c>
-      <c r="E15" t="n">
-        <v>18</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -881,15 +776,6 @@
           <t>Process of creating new input variables that better represent the underlying patterns in the data. It may include transformations (log, scaling), aggregations, interactions, temporal features, or domain-specific encodings. Effective feature engineering can significantly improve model performance even with simple algorithms. It embeds domain knowledge into the model and often provides more value than algorithmic complexity.  It is often one of the most impactful steps in the machine learning workflow.</t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v>19</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -913,15 +799,6 @@
 It is important to be in a position to Logically and Mathematically be in a position to defend inclusion and exclusion decisions. Although a highly technical step, it is critically important that stakeholders and partners are included and in references and terms which are appropriate for them.</t>
         </is>
       </c>
-      <c r="E17" t="n">
-        <v>20</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" t="n">
-        <v>6</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -944,15 +821,6 @@
           <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
         </is>
       </c>
-      <c r="E18" t="n">
-        <v>22</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="n">
-        <v>8</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -975,15 +843,6 @@
           <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
         </is>
       </c>
-      <c r="E19" t="n">
-        <v>23</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" t="n">
-        <v>9</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1006,15 +865,6 @@
           <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
         </is>
       </c>
-      <c r="E20" t="n">
-        <v>24</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="n">
-        <v>10</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1037,15 +887,6 @@
           <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
         </is>
       </c>
-      <c r="E21" t="n">
-        <v>25</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" t="n">
-        <v>11</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1068,15 +909,6 @@
           <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
         </is>
       </c>
-      <c r="E22" t="n">
-        <v>27</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" t="n">
-        <v>13</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1099,15 +931,6 @@
           <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
         </is>
       </c>
-      <c r="E23" t="n">
-        <v>28</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" t="n">
-        <v>14</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1130,15 +953,6 @@
           <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
         </is>
       </c>
-      <c r="E24" t="n">
-        <v>29</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1161,11 +975,6 @@
           <t>To Be Defined</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1184,13 +993,6 @@
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="n">
-        <v>21</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1209,13 +1011,6 @@
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="n">
-        <v>26</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1238,11 +1033,6 @@
           <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1265,11 +1055,6 @@
           <t>Process of explaining how a model makes predictions and which features influence its decisions. This may involve feature importance, partial dependence plots, SHAP values, or simpler surrogate models. Interpretability helps stakeholders understand, trust, and validate the model’s behavior. It is especially important in regulated or high-impact decision environments.</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1292,11 +1077,6 @@
           <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1319,11 +1099,6 @@
           <t>List used to manage the default order of items as stored in the Notes Sheet. Specifically, there is a heirarchical order created and expected to prioritize how items are stored and filter, this list maintains that order and can be used as guidance to understand.</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1346,11 +1121,6 @@
           <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1373,11 +1143,6 @@
           <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1400,11 +1165,6 @@
           <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1428,11 +1188,6 @@
 Similar to the process of engagement and audit followed in Feature Selection, it is critically important that actions are documented, defensible and clearly and consistently articulated to stakeholders in a meaningful manner.</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Streamlit/Data/defined_processes.xlsx
+++ b/Streamlit/Data/defined_processes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,119 +510,115 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Data Preparation</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
-        </is>
-      </c>
+          <t>Regularization</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Deployment</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Exploratory Data Analysis</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">Foundational step in ensuring the success of a machine learning model—and, by extension, the overall project. Its purpose is to confirm that the data is appropriately structured, consistent, and of sufficient quality to support reliable modeling.
 While every dataset and project is unique, applying a consistent EDA approach helps reduce the laborious and time-consuming nature of data preparation. A structured process enables quicker identification of data issues, improves understanding of key variables and relationships, and creates a more stable foundation for subsequent modeling decisions. </t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Feature Engineering</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Process of creating new input variables that better represent the underlying patterns in the data. It may include transformations (log, scaling), aggregations, interactions, temporal features, or domain-specific encodings. Effective feature engineering can significantly improve model performance even with simple algorithms. It embeds domain knowledge into the model and often provides more value than algorithmic complexity.  It is often one of the most impactful steps in the machine learning workflow.</t>
-        </is>
-      </c>
-    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Feature Engineering</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Process of creating new input variables that better represent the underlying patterns in the data. It may include transformations (log, scaling), aggregations, interactions, temporal features, or domain-specific encodings. Effective feature engineering can significantly improve model performance even with simple algorithms. It embeds domain knowledge into the model and often provides more value than algorithmic complexity.  It is often one of the most impactful steps in the machine learning workflow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>Process of identifying and retaining the most relevant variables for model training while removing redundant, noisy, or irrelevant features. This helps reduce overfitting, improve model performance, and increase interpretability. Feature selection techniques may be statistical, model-based, or embedded within the learning algorithm. The goal is to create a simpler, more robust feature set that generalizes well to new data.
 It is important to be in a position to Logically and Mathematically be in a position to defend inclusion and exclusion decisions. Although a highly technical step, it is critically important that stakeholders and partners are included and in references and terms which are appropriate for them.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Goal Setting</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
-        </is>
-      </c>
-    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hyperparameter Tuning</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -637,29 +633,29 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
+          <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Hyperparameter Tuning</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
+          <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
         </is>
       </c>
     </row>
@@ -676,12 +672,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
+          <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
         </is>
       </c>
     </row>
@@ -698,33 +694,55 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>Data Collection</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Data collection involves identifying, sourcing, and acquiring the datasets required to solve the defined problem. This may include internal databases, APIs, logs, third-party data, or manually collected data. Key considerations include data availability, coverage, granularity, freshness, and legal or privacy constraints. The quality and relevance of collected data fundamentally limit the ceiling of model performance.
 Need to understand the data available to solve a problem, insure that it's documented, understood and trusted. Need to identify, not only information which is available, but information which is not available and should be.  This should be explicitly documented, referenced constantly and readily available (Semantic and Functional Definition).</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>Data Preparation</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Data preparation focuses on cleaning and structuring raw data into a usable format for modeling. This includes handling missing values, correcting errors, standardizing formats, encoding categorical variables, and aligning labels with features. It also often involves train/validation/test splitting to prevent data leakage. This step is critical because most models assume clean, well-structured inputs and are highly sensitive to data issues.
 Need to establish up a consistent, robust and repeatable data ingestion process, which starts at the outset of the project. Where the infrastructure is not immediately available, need to clearly document the journey.  Need to call out requirements, expectations and limitations, and where resources are necessary, they should be identified at this point. 
@@ -732,51 +750,29 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>Exploratory Data Analysis</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t xml:space="preserve">Foundational step in ensuring the success of a machine learning model—and, by extension, the overall project. Its purpose is to confirm that the data is appropriately structured, consistent, and of sufficient quality to support reliable modeling.
 While every dataset and project is unique, applying a consistent EDA approach helps reduce the laborious and time-consuming nature of data preparation. A structured process enables quicker identification of data issues, improves understanding of key variables and relationships, and creates a more stable foundation for subsequent modeling decisions. </t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Feature Engineering</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Process of creating new input variables that better represent the underlying patterns in the data. It may include transformations (log, scaling), aggregations, interactions, temporal features, or domain-specific encodings. Effective feature engineering can significantly improve model performance even with simple algorithms. It embeds domain knowledge into the model and often provides more value than algorithmic complexity.  It is often one of the most impactful steps in the machine learning workflow.</t>
-        </is>
-      </c>
-    </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
@@ -790,38 +786,38 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>Feature Engineering</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Process of creating new input variables that better represent the underlying patterns in the data. It may include transformations (log, scaling), aggregations, interactions, temporal features, or domain-specific encodings. Effective feature engineering can significantly improve model performance even with simple algorithms. It embeds domain knowledge into the model and often provides more value than algorithmic complexity.  It is often one of the most impactful steps in the machine learning workflow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Process of identifying and retaining the most relevant variables for model training while removing redundant, noisy, or irrelevant features. This helps reduce overfitting, improve model performance, and increase interpretability. Feature selection techniques may be statistical, model-based, or embedded within the learning algorithm. The goal is to create a simpler, more robust feature set that generalizes well to new data.
 It is important to be in a position to Logically and Mathematically be in a position to defend inclusion and exclusion decisions. Although a highly technical step, it is critically important that stakeholders and partners are included and in references and terms which are appropriate for them.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
-        </is>
-      </c>
-    </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
@@ -835,12 +831,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hyperparameter Tuning</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
+          <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
         </is>
       </c>
     </row>
@@ -857,12 +853,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Model Evaluation</t>
+          <t>Hyperparameter Tuning</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
+          <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
         </is>
       </c>
     </row>
@@ -879,12 +875,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Model Evaluation</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
+          <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
         </is>
       </c>
     </row>
@@ -901,12 +897,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
+          <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
         </is>
       </c>
     </row>
@@ -923,12 +919,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Model Interpretability</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
+          <t>Process of explaining how a model makes predictions and which features influence its decisions. This may involve feature importance, partial dependence plots, SHAP values, or simpler surrogate models. Interpretability helps stakeholders understand, trust, and validate the model’s behavior. It is especially important in regulated or high-impact decision environments.</t>
         </is>
       </c>
     </row>
@@ -945,12 +941,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bias, Fairness, and Ethics</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
+          <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
         </is>
       </c>
     </row>
@@ -962,17 +958,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>To Be Defined</t>
+          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
         </is>
       </c>
     </row>
@@ -989,10 +985,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Model Selection</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>Bias, Fairness, and Ethics</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1002,42 +1002,42 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Model Summarization / Model Interpretability</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>To Be Defined</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Model Evaluation</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
-        </is>
-      </c>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Model Summarization / Model Interpretability</t>
+          <t>Model Evaluation</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1052,36 +1052,32 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Process of explaining how a model makes predictions and which features influence its decisions. This may involve feature importance, partial dependence plots, SHAP values, or simpler surrogate models. Interpretability helps stakeholders understand, trust, and validate the model’s behavior. It is especially important in regulated or high-impact decision environments.</t>
+          <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Model Evaluation</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
-        </is>
-      </c>
+          <t>Test Relative to Baseline</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Organization - Definition</t>
+          <t>Model Interpretability</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1096,36 +1092,32 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>List used to manage the default order of items as stored in the Notes Sheet. Specifically, there is a heirarchical order created and expected to prioritize how items are stored and filter, this list maintains that order and can be used as guidance to understand.</t>
+          <t>Process of explaining how a model makes predictions and which features influence its decisions. This may involve feature importance, partial dependence plots, SHAP values, or simpler surrogate models. Interpretability helps stakeholders understand, trust, and validate the model’s behavior. It is especially important in regulated or high-impact decision environments.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Model Selection</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
-        </is>
-      </c>
+          <t>Define Baseline</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1140,14 +1132,14 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
+          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Organization - Definition</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1162,27 +1154,93 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
+          <t>List used to manage the default order of items as stored in the Notes Sheet. Specifically, there is a heirarchical order created and expected to prioritize how items are stored and filter, this list maintains that order and can be used as guidance to understand.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>Validation/ Model Selection</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>The process of choosing the most appropriate algorithm or model type for a given problem and dataset. This decision is based on factors such as data size, feature structure, interpretability needs, computational constraints, and performance requirements. Multiple candidate models are often tested and compared using consistent evaluation methods. The objective is to identify the model that provides the best balance between accuracy, stability, and practical usability.
 Similar to the process of engagement and audit followed in Feature Selection, it is critically important that actions are documented, defensible and clearly and consistently articulated to stakeholders in a meaningful manner.</t>

--- a/Streamlit/Data/defined_processes.xlsx
+++ b/Streamlit/Data/defined_processes.xlsx
@@ -523,7 +523,11 @@
           <t>Regularization</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Explain what this means from a practical application of what needs to be done for the proces.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">

--- a/Streamlit/Data/defined_processes.xlsx
+++ b/Streamlit/Data/defined_processes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D107"/>
+  <dimension ref="A1:D123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,48 +783,44 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Persuasion</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Data Collection</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>Data collection involves identifying, sourcing, and acquiring the datasets required to solve the defined problem. This may include internal databases, APIs, logs, third-party data, or manually collected data. Key considerations include data availability, coverage, granularity, freshness, and legal or privacy constraints. The quality and relevance of collected data fundamentally limit the ceiling of model performance.
 Need to understand the data available to solve a problem, insure that it's documented, understood and trusted. Need to identify, not only information which is available, but information which is not available and should be.  This should be explicitly documented, referenced constantly and readily available (Semantic and Functional Definition).</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Data Collection</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Label Data</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Ensure that All data is defined, and classified. Including Semantic and Functional Definitions.</t>
-        </is>
-      </c>
-    </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
@@ -838,32 +834,72 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ensure Sufficient Data Exists</t>
+          <t>Label Data</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ensure that model has sufficient representation (Covered from at a Minimum Semantic and Functional Perspective).</t>
+          <t>Ensure that All data is defined, and classified. Including Semantic and Functional Definitions.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Data Collection</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ensure Sufficient Data Exists</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Ensure that model has sufficient representation (Covered from at a Minimum Semantic and Functional Perspective).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Data Engineering</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Data Preparation</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>Data preparation focuses on cleaning and structuring raw data into a usable format for modeling. This includes handling missing values, correcting errors, standardizing formats, encoding categorical variables, and aligning labels with features. It also often involves train/validation/test splitting to prevent data leakage. This step is critical because most models assume clean, well-structured inputs and are highly sensitive to data issues.
 Need to establish up a consistent, robust and repeatable data ingestion process, which starts at the outset of the project. Where the infrastructure is not immediately available, need to clearly document the journey.  Need to call out requirements, expectations and limitations, and where resources are necessary, they should be identified at this point. 
@@ -871,54 +907,10 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Data Preparation</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Regularization</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Explain what this means from a practical application of what needs to be done for the proces.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Deployment</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
-        </is>
-      </c>
-    </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Data Preparation</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -928,41 +920,37 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Package Model for Deployment with everything necessary</t>
+          <t>Regularization</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Package the model with all required preprocessing steps. Ensures predictions in production match training conditions.</t>
+          <t>Explain what this means from a practical application of what needs to be done for the proces.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Decision Making</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Test in different environments</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Test the model in a staging or test environment. Utilize Dedicated Environment. Reduces risk of failures in production.</t>
-        </is>
-      </c>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Decision Making</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -972,259 +960,255 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Version Control</t>
+          <t>Identify Criteria</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Create a versioned and reproducible deployment artifact. Supports rollback, auditing, and maintenance.</t>
+          <t>Always identify multiple criteria, how can we fairly compare approaches.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Decision Making</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Identify Evaluation Framework</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Deployment</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Deployment</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Package Model for Deployment with everything necessary</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Package the model with all required preprocessing steps. Ensures predictions in production match training conditions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Deployment</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Test in different environments</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Test the model in a staging or test environment. Utilize Dedicated Environment. Reduces risk of failures in production.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Deployment</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Version Control</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Create a versioned and reproducible deployment artifact. Supports rollback, auditing, and maintenance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>Exploratory Data Analysis</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t xml:space="preserve">Foundational step in ensuring the success of a machine learning model—and, by extension, the overall project. Its purpose is to confirm that the data is appropriately structured, consistent, and of sufficient quality to support reliable modeling.
 While every dataset and project is unique, applying a consistent EDA approach helps reduce the laborious and time-consuming nature of data preparation. A structured process enables quicker identification of data issues, improves understanding of key variables and relationships, and creates a more stable foundation for subsequent modeling decisions. </t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Feature Engineering</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>Process of creating new input variables that better represent the underlying patterns in the data. It may include transformations (log, scaling), aggregations, interactions, temporal features, or domain-specific encodings. Effective feature engineering can significantly improve model performance even with simple algorithms. It embeds domain knowledge into the model and often provides more value than algorithmic complexity.  It is often one of the most impactful steps in the machine learning workflow.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Feature Engineering</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
         <is>
           <t>Ratios or Observed Values</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>What ratios or proportions could better represent behavior than raw values? Many real-world patterns depend on relative size (e.g., debt-to-income, usage-to-capacity), so ratios often reveal signal that absolute values hide.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Feature Engineering</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
         <is>
           <t>Include Interactions</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>What combinations or interactions might reflect how factors work together? Some outcomes are driven by the interaction between variables (e.g., high balance and high transaction frequency), so combining features can expose relationships a model might miss.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Feature Engineering</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
         <is>
           <t>How does Time Impact?</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>What time-based changes or aggregates could capture trends or stability? Differences, growth rates, or rolling averages often reflect momentum or consistency, which are strong predictors of future behavior.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>Process of identifying and retaining the most relevant variables for model training while removing redundant, noisy, or irrelevant features. This helps reduce overfitting, improve model performance, and increase interpretability. Feature selection techniques may be statistical, model-based, or embedded within the learning algorithm. The goal is to create a simpler, more robust feature set that generalizes well to new data.
 It is important to be in a position to Logically and Mathematically be in a position to defend inclusion and exclusion decisions. Although a highly technical step, it is critically important that stakeholders and partners are included and in references and terms which are appropriate for them.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Feature Selection</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Explain Feature Practical Relevance</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Generate feature importance or explanation outputs. Helps understand what drives model predictions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Feature Selection</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Remove Unnecessary Features</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Remove features with high missingness or low variance. Reduces noise and improves model stability.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Feature Selection</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Understand Feature Correlations</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Check for multicollinearity or redundant features. Helps prevent unstable models and improves interpretability.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Feature Selection</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Document Feature Statistical Relevance</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Validate selected features using model or statistical methods. Ensures the retained features actually contribute to predictive performance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Feature Selection</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Test Individual Feature Importance</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Need to understand how much an individual feature contributes beyond what the other features already provide. A feature has incremental value and removing or disrupting it should decrease performance. This supports inclusion of value add feature, opposed to those which create redundancy or noise.</t>
-        </is>
-      </c>
-    </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
@@ -1238,10 +1222,120 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
+          <t>Explain Feature Practical Relevance</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Generate feature importance or explanation outputs. Helps understand what drives model predictions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Feature Selection</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Remove Unnecessary Features</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Remove features with high missingness or low variance. Reduces noise and improves model stability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Feature Selection</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Understand Feature Correlations</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Check for multicollinearity or redundant features. Helps prevent unstable models and improves interpretability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Feature Selection</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Document Feature Statistical Relevance</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Validate selected features using model or statistical methods. Ensures the retained features actually contribute to predictive performance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Feature Selection</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Test Individual Feature Importance</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Need to understand how much an individual feature contributes beyond what the other features already provide. A feature has incremental value and removing or disrupting it should decrease performance. This supports inclusion of value add feature, opposed to those which create redundancy or noise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Feature Selection</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>Reconstruction Error in Autoencoders</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>Does this feature improve the model’s ability to represent and reconstruct the data? An autoencoder learns to compress the input data into a smaller latent representation and then reconstruct the original data. Reconstruction error measures the difference between the original observations and the reconstructed output; lower error generally means the model has preserved more of the data’s structure.
 For feature selection, you can remove, mask, or add one feature at a time and observe how reconstruction error changes. A substantial increase in error after removing a feature suggests that the feature contains important information, although highly correlated features may appear less important because another feature can reconstruct the same information.
@@ -1249,23 +1343,23 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
         <is>
           <t>Mutual Information with Latent Cluster Assignment</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>How strongly is this feature associated with the cluster structure the model discovered? Mutual information measures how much knowing one variable reduces uncertainty about another. In this context, it measures the association between a feature and the cluster labels produced by an unsupervised model.
 For feature selection, features with high mutual information are strongly associated with the discovered cluster structure and may be useful for distinguishing groups. Features with very low mutual information may contribute little to the final segmentation, although they could still affect the clustering indirectly through interactions with other features.
@@ -1273,23 +1367,23 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
         <is>
           <t>Permutation for Clustering</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>Permutation importance measures the value of a feature by randomly shuffling its values while leaving the other features unchanged. Shuffling breaks the feature’s relationship with the observations; if cluster quality, assignment consistency, or model performance worsens, the feature was contributing useful information.
 For feature selection, features that cause a large decline in clustering performance when shuffled are considered important. Features whose permutation has little effect may be redundant, irrelevant, or dominated by stronger features and could be candidates for removal.
@@ -1298,160 +1392,50 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>General Expectations</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Goal Setting</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Hyperparameter Tuning</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Hyperparameter Tuning</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Define Search Space</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Define a clear search space for key hyperparameters. Ensures tuning focuses on meaningful configurations.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Hyperparameter Tuning</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Cross Validation to Prevent Overfitting</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Use cross-validation or a validation set for tuning. Prevents overfitting to the training data.</t>
-        </is>
-      </c>
-    </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Hyperparameter Tuning</t>
+          <t>General Expectations</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Document Results</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Record best parameters and associated performance. Allows reproducibility and comparison across experiments.</t>
-        </is>
-      </c>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Hyperparameter Tuning</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Explicit Exploration. Avoid needless and endless tuning</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Define Parameters you will tune and approach to tuning before you commence tuning. Do not simply tune model to optimal parameters without considering what you are actually doing, and its ability to generalize.</t>
+          <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Hyperparameter Tuning</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1466,14 +1450,14 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>To Be Defined</t>
+          <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Hyperparameter Tuning</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1483,19 +1467,19 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Define Search Space</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
+          <t>Define a clear search space for key hyperparameters. Ensures tuning focuses on meaningful configurations.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Hyperparameter Tuning</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1505,55 +1489,165 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Cross Validation to Prevent Overfitting</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
+          <t>Use cross-validation or a validation set for tuning. Prevents overfitting to the training data.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>Hyperparameter Tuning</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Document Results</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Record best parameters and associated performance. Allows reproducibility and comparison across experiments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Hyperparameter Tuning</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Explicit Exploration. Avoid needless and endless tuning</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Define Parameters you will tune and approach to tuning before you commence tuning. Do not simply tune model to optimal parameters without considering what you are actually doing, and its ability to generalize.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>Machine Learning Lifecycle</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>To Be Defined</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Goal Setting</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
         <is>
           <t>Data Collection</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>Data collection involves identifying, sourcing, and acquiring the datasets required to solve the defined problem. This may include internal databases, APIs, logs, third-party data, or manually collected data. Key considerations include data availability, coverage, granularity, freshness, and legal or privacy constraints. The quality and relevance of collected data fundamentally limit the ceiling of model performance.
 Need to understand the data available to solve a problem, insure that it's documented, understood and trusted. Need to identify, not only information which is available, but information which is not available and should be.  This should be explicitly documented, referenced constantly and readily available (Semantic and Functional Definition).</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>Machine Learning Lifecycle</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
         <is>
           <t>Data Preparation</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>Data preparation focuses on cleaning and structuring raw data into a usable format for modeling. This includes handling missing values, correcting errors, standardizing formats, encoding categorical variables, and aligning labels with features. It also often involves train/validation/test splitting to prevent data leakage. This step is critical because most models assume clean, well-structured inputs and are highly sensitive to data issues.
 Need to establish up a consistent, robust and repeatable data ingestion process, which starts at the outset of the project. Where the infrastructure is not immediately available, need to clearly document the journey.  Need to call out requirements, expectations and limitations, and where resources are necessary, they should be identified at this point. 
@@ -1561,207 +1655,97 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>Machine Learning Lifecycle</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
         <is>
           <t>Exploratory Data Analysis</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t xml:space="preserve">Foundational step in ensuring the success of a machine learning model—and, by extension, the overall project. Its purpose is to confirm that the data is appropriately structured, consistent, and of sufficient quality to support reliable modeling.
 While every dataset and project is unique, applying a consistent EDA approach helps reduce the laborious and time-consuming nature of data preparation. A structured process enables quicker identification of data issues, improves understanding of key variables and relationships, and creates a more stable foundation for subsequent modeling decisions. </t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>Machine Learning Lifecycle</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
         <is>
           <t>Feature Engineering</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>Process of creating new input variables that better represent the underlying patterns in the data. It may include transformations (log, scaling), aggregations, interactions, temporal features, or domain-specific encodings. Effective feature engineering can significantly improve model performance even with simple algorithms. It embeds domain knowledge into the model and often provides more value than algorithmic complexity.  It is often one of the most impactful steps in the machine learning workflow.</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>Machine Learning Lifecycle</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>Process of identifying and retaining the most relevant variables for model training while removing redundant, noisy, or irrelevant features. This helps reduce overfitting, improve model performance, and increase interpretability. Feature selection techniques may be statistical, model-based, or embedded within the learning algorithm. The goal is to create a simpler, more robust feature set that generalizes well to new data.
 It is important to be in a position to Logically and Mathematically be in a position to defend inclusion and exclusion decisions. Although a highly technical step, it is critically important that stakeholders and partners are included and in references and terms which are appropriate for them.</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>Machine Learning Lifecycle</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>The process of choosing the most appropriate algorithm or model type for a given problem and dataset. This decision is based on factors such as data size, feature structure, interpretability needs, computational constraints, and performance requirements. Multiple candidate models are often tested and compared using consistent evaluation methods. The objective is to identify the model that provides the best balance between accuracy, stability, and practical usability.
 Similar to the process of engagement and audit followed in Feature Selection, it is critically important that actions are documented, defensible and clearly and consistently articulated to stakeholders in a meaningful manner.</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Hyperparameter Tuning</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Model Evaluation</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Validation</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Model Interpretability</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Process of explaining how a model makes predictions and which features influence its decisions. This may involve feature importance, partial dependence plots, SHAP values, or simpler surrogate models. Interpretability helps stakeholders understand, trust, and validate the model’s behavior. It is especially important in regulated or high-impact decision environments.</t>
-        </is>
-      </c>
-    </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
@@ -1775,12 +1759,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
+          <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
         </is>
       </c>
     </row>
@@ -1797,12 +1781,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Hyperparameter Tuning</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
+          <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
         </is>
       </c>
     </row>
@@ -1819,85 +1803,85 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bias, Fairness, and Ethics</t>
+          <t>Model Evaluation</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
+          <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Measuing Effectiveness</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>How can one measure how effective/ineffective a particular communication was?</t>
+          <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Message Spareness</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Model Interpretability</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Utilize a less is more approach, whether that is Slides, Words, Pages, Etc. Less is more.</t>
+          <t>Process of explaining how a model makes predictions and which features influence its decisions. This may involve feature importance, partial dependence plots, SHAP values, or simpler surrogate models. Interpretability helps stakeholders understand, trust, and validate the model’s behavior. It is especially important in regulated or high-impact decision environments.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Model Evaluation</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
+          <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Model Evaluation</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1907,148 +1891,148 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Test Relative to Baseline</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Bias, Fairness, and Ethics</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Measuing Effectiveness</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>How can one measure how effective/ineffective a particular communication was?</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Message Spareness</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Utilize a less is more approach, whether that is Slides, Words, Pages, Etc. Less is more.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>Model Evaluation</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Model Evaluation</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Test Relative to Baseline</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Model Evaluation</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
         <is>
           <t>Use Relevant Metrics</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>Use metrics appropriate to the problem type and business goal. Ensures the model is evaluated in a way that reflects real-world impact.
 This should change to be more specific. Define Thresholds. Test Thresholds, recommend based on X.</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Model Evaluation</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Keep Hold Out</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Evaluate performance on a hold-out test set. Provides an unbiased estimate of generalization performance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Model Evaluation</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Review Overfitting</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Check for overfitting by comparing training and test results. Identifies models that may not perform well in production.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Model Interpretability</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Process of explaining how a model makes predictions and which features influence its decisions. This may involve feature importance, partial dependence plots, SHAP values, or simpler surrogate models. Interpretability helps stakeholders understand, trust, and validate the model’s behavior. It is especially important in regulated or high-impact decision environments.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Model Interpretability</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Explain Selected Features using Words</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Utilize feature importance metrics to visualize and explain.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Model Interpretability</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Results/Outcome should not be shocking</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">This should be a formal step as engagement along the way is predicated on this as a core tenet and principle. If people seem shocked, embed stronger components earlier in process. </t>
-        </is>
-      </c>
-    </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Model Interpretability</t>
+          <t>Model Evaluation</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2058,144 +2042,148 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Document Beyond Communciation</t>
+          <t>Keep Hold Out</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Document model behavior and major drivers. Supports stakeholder understanding and auditability.</t>
+          <t>Evaluate performance on a hold-out test set. Provides an unbiased estimate of generalization performance.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>Model Evaluation</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Review Overfitting</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Check for overfitting by comparing training and test results. Identifies models that may not perform well in production.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Model Interpretability</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Process of explaining how a model makes predictions and which features influence its decisions. This may involve feature importance, partial dependence plots, SHAP values, or simpler surrogate models. Interpretability helps stakeholders understand, trust, and validate the model’s behavior. It is especially important in regulated or high-impact decision environments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Model Interpretability</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Explain Selected Features using Words</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Utilize feature importance metrics to visualize and explain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Model Interpretability</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Results/Outcome should not be shocking</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This should be a formal step as engagement along the way is predicated on this as a core tenet and principle. If people seem shocked, embed stronger components earlier in process. </t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Model Interpretability</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Document Beyond Communciation</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Document model behavior and major drivers. Supports stakeholder understanding and auditability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
         <is>
           <t>The process of choosing the most appropriate algorithm or model type for a given problem and dataset. This decision is based on factors such as data size, feature structure, interpretability needs, computational constraints, and performance requirements. Multiple candidate models are often tested and compared using consistent evaluation methods. The objective is to identify the model that provides the best balance between accuracy, stability, and practical usability.
 Similar to the process of engagement and audit followed in Feature Selection, it is critically important that actions are documented, defensible and clearly and consistently articulated to stakeholders in a meaningful manner.</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Model Selection</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Define Baseline</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Model Selection</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Document Results and Choice</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Ensure that final selection is documented and agreed by appropriate stakeholders, who have been part of entire development journey, understand and are aware.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Model Selection</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Define Validation Approach in Advance</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Use cross-validation or a structured validation approach. Provides a more reliable estimate of model performance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Model Selection</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Validate no Leakage</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Ensure no data leakage between training and validation sets. Prevents overly optimistic performance estimates.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Model Selection</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Validate consistency over time</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Confirm performance stability across folds or time splits. Indicates the model is robust and generalizable.</t>
-        </is>
-      </c>
-    </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
@@ -2209,14 +2197,10 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>How will Model Learn?</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Must select an appropriate learning method. Supervised, Unsupervised, Semi-Supervised, Reinforcement</t>
-        </is>
-      </c>
+          <t>Define Baseline</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2231,12 +2215,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>What Problem is the Model Solving?</t>
+          <t>Document Results and Choice</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Must select an appropriate method. Classification, Regression, Clustering, Dimensionality Reduction, etc.</t>
+          <t>Ensure that final selection is documented and agreed by appropriate stakeholders, who have been part of entire development journey, understand and are aware.</t>
         </is>
       </c>
     </row>
@@ -2253,12 +2237,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>What Model/Algo is being used to solve the problem</t>
+          <t>Define Validation Approach in Advance</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Document founational assessment at the outset, can revisit during Model Selection.</t>
+          <t>Use cross-validation or a structured validation approach. Provides a more reliable estimate of model performance.</t>
         </is>
       </c>
     </row>
@@ -2275,10 +2259,120 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
+          <t>Validate no Leakage</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Ensure no data leakage between training and validation sets. Prevents overly optimistic performance estimates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Validate consistency over time</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Confirm performance stability across folds or time splits. Indicates the model is robust and generalizable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>How will Model Learn?</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Must select an appropriate learning method. Supervised, Unsupervised, Semi-Supervised, Reinforcement</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>What Problem is the Model Solving?</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Must select an appropriate method. Classification, Regression, Clustering, Dimensionality Reduction, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>What Model/Algo is being used to solve the problem</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Document founational assessment at the outset, can revisit during Model Selection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
           <t>Select Model(s) based on Objective</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t xml:space="preserve">Define what the objective of the model work is, state what is being measured and why. 
 Document all models which will be considered, including why they are appropriate and where models are excluded, insure rationale available. Compare multiple model types using the same validation approach. Ensures a fair comparison and better-informed model choice.
@@ -2286,142 +2380,32 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Model Selection</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Create and Understand Baseline</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Create Simplified Baseline Model, use this are reference. Ensure that this is communicated to Stakeholders, so they understand both the benchmark and expectation, to determine relevance. Should align with Goals.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Model Selection</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Performance vs Cost vs Practicality</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Consider interpretability, performance, and computational cost. Balances practical constraints with predictive accuracy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Model Selection</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>How Many Examples are Needed?</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Distinct for every type of Method or approach. Need to be comfortable that the dataset has enough examples and that they represent a population to which you believe is representive.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Monitoring</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Organization - Definition</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>List used to manage the default order of items as stored in the Notes Sheet. Specifically, there is a heirarchical order created and expected to prioritize how items are stored and filter, this list maintains that order and can be used as guidance to understand.</t>
-        </is>
-      </c>
-    </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Model Selection</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Create and Understand Baseline</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
+          <t>Create Simplified Baseline Model, use this are reference. Ensure that this is communicated to Stakeholders, so they understand both the benchmark and expectation, to determine relevance. Should align with Goals.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Model Selection</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2431,19 +2415,19 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Desired State Metrics</t>
+          <t>Performance vs Cost vs Practicality</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
+          <t>Consider interpretability, performance, and computational cost. Balances practical constraints with predictive accuracy.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Model Selection</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2453,85 +2437,81 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Current State Analysis</t>
+          <t>How Many Examples are Needed?</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
+          <t>Distinct for every type of Method or approach. Need to be comfortable that the dataset has enough examples and that they represent a population to which you believe is representive.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Root Cause Assessment</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
+          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Organization - Definition</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Historical Overview</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
+          <t>List used to manage the default order of items as stored in the Notes Sheet. Specifically, there is a heirarchical order created and expected to prioritize how items are stored and filter, this list maintains that order and can be used as guidance to understand.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Persuasion</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Baseline Metrics (Current State)</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
-        </is>
-      </c>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Re-enforce the Message</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2544,34 +2524,38 @@
           <t>Definition</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Desired State Metrics</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
+          <t>Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2581,19 +2565,19 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Train, Test, Validation Split</t>
+          <t>Current State Analysis</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Is split between Training, Testing and Validation appropriate, fair and responsible. Validate and document.</t>
+          <t>Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2603,19 +2587,19 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Convergence Achieved?</t>
+          <t>Root Cause Assessment</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Verify model converges and loss decreases during training. Confirms the model is learning meaningful patterns.</t>
+          <t>Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2625,37 +2609,41 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Logging of Parameters</t>
+          <t>Historical Overview</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Log model parameters, features, training configuration and results. Supports reproducibility and troubleshooting.</t>
+          <t>Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Understand Your Audience</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
+          <t>Baseline Metrics (Current State)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Understand Your Message</t>
+          <t>Re-enforce the Message</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2673,7 +2661,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Understand Your Strategy</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2688,45 +2676,385 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Beyond understanding Your Message, you need to think about how you are going to articulate your story, your goals, motivation, priority. Reconizing differences between things that have great personal meaning, business relevance, or simply mandated work.</t>
+          <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Understand Your Visuals</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
+          <t>Train, Test, Validation Split</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Is split between Training, Testing and Validation appropriate, fair and responsible. Validate and document.</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Convergence Achieved?</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Verify model converges and loss decreases during training. Confirms the model is learning meaningful patterns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Logging of Parameters</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Log model parameters, features, training configuration and results. Supports reproducibility and troubleshooting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Activation Function</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Select a Activation Function based on Learning Paradigm and Method, potentially trying multiple variants across grid search.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Understand Your Audience</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Understand Your Audience</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Who is it?</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>It might be extremely broad, it might change for a similiar piece of work, or the work might be done with a single person in mind, and little focus or regard is paid to others, regardless of the level of interaction to which they will have.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Understand Your Audience</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>What do they want?</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The more we know about the motivations and incentives of decision makers, the more we can control the communication. </t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Understand Your Audience</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Are they likely to Care?</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Understand Your Message</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Understand Your Message</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Do you actually understand it?</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>You must understand it, backforward and center. Message, Purpose. Reason. All can be different, might have different motivations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Understand Your Message</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Clarity for all.</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Is the message clear to you, will it be clear to them?</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Understand Your Message</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>BLUF</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Bottom Line Up Front</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Understand Your Message</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Tell the Story, Do not Show it.</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Storytelling beats data 100% of the time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Understand Your Message</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Where are you truly at?</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Is the glass half full, half empty. If it's half full, do you have what you really want in the glass?</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Understand Your Strategy</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Beyond understanding Your Message, you need to think about how you are going to articulate your story, your goals, motivation, priority. Reconizing differences between things that have great personal meaning, business relevance, or simply mandated work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Understand Your Visuals</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Understand Your Visuals</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Simplicity over Complexity</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Are they Simple and Clear?</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
           <t>Validation</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
         <is>
           <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
         </is>
